--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260207_201351.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260207_201351.xlsx
@@ -5548,7 +5548,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260207_201351.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260207_201351.xlsx
@@ -5548,7 +5548,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
